--- a/4_outputs/final/Table13.xlsx
+++ b/4_outputs/final/Table13.xlsx
@@ -417,58 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>Rank</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Canonical</t>
+          <t>Config</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SWD</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Chamfer</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Hausdorff</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Gauss. W_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Grassmann</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>linear MMD</t>
+          <t>CV macro-F1</t>
         </is>
       </c>
     </row>
@@ -480,37 +450,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>MLP 3L/256h, lr=0.0003 (best)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.509</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.600</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0.684</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3.727</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.067</t>
+          <t>0.8192 ± 0.0032</t>
         </is>
       </c>
     </row>
@@ -522,37 +467,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>MLP 2L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.388</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.454</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0.618</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3.629</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.057</t>
+          <t>0.8184 ± 0.0030</t>
         </is>
       </c>
     </row>
@@ -564,37 +484,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>MLP 6L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.011</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.454</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0.581</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0.717</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3.717</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.129</t>
+          <t>0.8183 ± 0.0023</t>
         </is>
       </c>
     </row>
@@ -606,37 +501,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>MLP 2L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.487</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0.607</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3.307</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.096</t>
+          <t>0.8183 ± 0.0022</t>
         </is>
       </c>
     </row>
@@ -648,37 +518,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>MLP 4L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.429</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.529</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.646</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3.514</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.095</t>
+          <t>0.8181 ± 0.0017</t>
         </is>
       </c>
     </row>
@@ -690,37 +535,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.130</t>
+          <t>MLP 2L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.417</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.639</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>3.598</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.080</t>
+          <t>0.8180 ± 0.0038</t>
         </is>
       </c>
     </row>
@@ -732,37 +552,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.170</t>
+          <t>MLP 3L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.427</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.522</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.687</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>3.729</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.105</t>
+          <t>0.8176 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -774,37 +569,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>MLP 4L/384h, lr=0.0003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.474</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.564</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.658</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3.566</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.065</t>
+          <t>0.8175 ± 0.0017</t>
         </is>
       </c>
     </row>
@@ -816,37 +586,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>MLP 4L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.430</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.556</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.671</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>3.444</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.104</t>
+          <t>0.8169 ± 0.0024</t>
         </is>
       </c>
     </row>
@@ -858,37 +603,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>MLP 6L/256h, lr=0.0003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.517</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.617</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>3.343</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.062</t>
+          <t>0.8168 ± 0.0026</t>
         </is>
       </c>
     </row>
@@ -900,37 +620,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>MLP 3L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.446</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.542</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.677</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>3.484</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.091</t>
+          <t>0.8165 ± 0.0030</t>
         </is>
       </c>
     </row>
@@ -942,37 +637,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>MLP 2L/384h, lr=0.001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0.467</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.566</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.677</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>3.462</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.094</t>
+          <t>0.8162 ± 0.0053</t>
         </is>
       </c>
     </row>
@@ -984,37 +654,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>MLP 6L/384h, lr=0.001</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0.417</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.498</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0.667</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3.667</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.117</t>
+          <t>0.8156 ± 0.0039</t>
         </is>
       </c>
     </row>
@@ -1026,37 +671,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>MLP 6L/256h, lr=0.001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>0.415</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.510</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.675</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3.753</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.098</t>
+          <t>0.8153 ± 0.0027</t>
         </is>
       </c>
     </row>
@@ -1068,37 +688,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>MLP 4L/384h, lr=0.001</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.008</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0.394</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.464</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.578</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>3.421</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.056</t>
+          <t>0.8151 ± 0.0024</t>
         </is>
       </c>
     </row>
@@ -1110,37 +705,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>MLP 3L/384h, lr=0.001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.010</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0.417</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.520</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.640</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>3.333</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.103</t>
+          <t>0.8151 ± 0.0015</t>
         </is>
       </c>
     </row>
@@ -1152,79 +722,267 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>LR C=3.0, cw=None (chosen)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.009</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>0.461</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.490</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.595</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2.993</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.104</t>
+          <t>0.8101 ± 0.0020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ρ vs. canonical</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>LR C=2.0, cw=None</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.525</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0.485</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.444</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-0.243</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>0.620</t>
+          <t>0.8098 ± 0.0018</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LR C=5.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.8097 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LR C=1.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.8087 ± 0.0025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LR C=3.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.8079 ± 0.0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LR C=2.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.8077 ± 0.0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LR C=10.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.8075 ± 0.0020</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LR C=5.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.8073 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LR C=1.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.8069 ± 0.0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LR C=10.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.8063 ± 0.0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LR C=30.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.8039 ± 0.0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LR C=30.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.8022 ± 0.0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LR C=100.0, cw=None</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.7967 ± 0.0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LR C=100.0, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.7942 ± 0.0017</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LR C=0.1, cw=balanced</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.7919 ± 0.0032</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LR C=0.1, cw=None</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.7904 ± 0.0032</t>
         </is>
       </c>
     </row>

--- a/4_outputs/final/Table13.xlsx
+++ b/4_outputs/final/Table13.xlsx
@@ -417,572 +417,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Config</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>CV macro-F1</t>
-        </is>
-      </c>
+          <t>Corpus mean</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Load-bearing?</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Mega-doc vs rest</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MLP 3L/256h, lr=0.0003 (best)</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.8192 ± 0.0032</t>
+          <t>Research</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Mega-doc</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Rest</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Hedge rate (/1k words)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MLP 2L/256h, lr=0.0003</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.8184 ± 0.0030</t>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R &gt; P</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1.14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Deontic (must/should) rate (/1k words)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MLP 6L/384h, lr=0.0003</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0023</t>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>P &gt; R</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.94</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Passive-voice rate (/1k words)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MLP 2L/384h, lr=0.0003</t>
+          <t>8.45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.8183 ± 0.0022</t>
+          <t>10.30</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R &gt; P</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>9.77</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Mean sentence length (words)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MLP 4L/256h, lr=0.001</t>
+          <t>63.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.8181 ± 0.0017</t>
+          <t>37.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P &gt; R</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>276.9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>35.6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>First-person rate (/1k words)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MLP 2L/256h, lr=0.001</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.8180 ± 0.0038</t>
+          <t>6.90</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>≈</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>5.88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Nominalisation rate (/1k words)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MLP 3L/384h, lr=0.0003</t>
+          <t>39.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.8176 ± 0.0015</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MLP 4L/384h, lr=0.0003</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.8175 ± 0.0017</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MLP 4L/256h, lr=0.0003</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.8169 ± 0.0024</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MLP 6L/256h, lr=0.0003</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.8168 ± 0.0026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MLP 3L/256h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.8165 ± 0.0030</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MLP 2L/384h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0.8162 ± 0.0053</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MLP 6L/384h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.8156 ± 0.0039</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MLP 6L/256h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>0.8153 ± 0.0027</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MLP 4L/384h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0.8151 ± 0.0024</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MLP 3L/384h, lr=0.001</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.8151 ± 0.0015</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LR C=3.0, cw=None (chosen)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0.8101 ± 0.0020</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>LR C=2.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0.8098 ± 0.0018</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>LR C=5.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0.8097 ± 0.0017</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>LR C=1.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0.8087 ± 0.0025</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>LR C=3.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0.8079 ± 0.0014</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>LR C=2.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>0.8077 ± 0.0016</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>LR C=10.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0.8075 ± 0.0020</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>LR C=5.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.8073 ± 0.0017</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>LR C=1.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0.8069 ± 0.0026</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>LR C=10.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0.8063 ± 0.0013</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>LR C=30.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>0.8039 ± 0.0023</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>LR C=30.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0.8022 ± 0.0016</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>LR C=100.0, cw=None</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0.7967 ± 0.0010</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>LR C=100.0, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0.7942 ± 0.0017</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>LR C=0.1, cw=balanced</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>0.7919 ± 0.0032</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>LR C=0.1, cw=None</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0.7904 ± 0.0032</t>
+          <t>36.37</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>≈</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20.02</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>38.84</t>
         </is>
       </c>
     </row>
